--- a/report_forms/043_customer_incident_form--report_forms.xlsx
+++ b/report_forms/043_customer_incident_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -811,8 +811,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -840,12 +840,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'incidents':_'damage'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'Incidents': 'Damage'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'incidents':_'quality_issue'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'Incidents': 'Quality issue'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'incidents':_'defective_product'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'Incidents': 'Defective product'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'customer_name',_'value':_'customer_name'}</t>
+          <t>customer_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Customer name', 'value': 'customer_name'}</t>
+          <t>Customer name</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'contact_person',_'value':_'contact_person'}</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Contact person', 'value': 'contact_person'}</t>
+          <t>Contact person</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'phone_number',_'value':_'phone_number'}</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Phone number', 'value': 'phone_number'}</t>
+          <t>Phone number</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'signed',_'value':_'signed'}</t>
+          <t>signed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Signed', 'value': 'signed'}</t>
+          <t>Signed</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'unsigned',_'value':_'unsigned'}</t>
+          <t>unsigned</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Unsigned', 'value': 'unsigned'}</t>
+          <t>Unsigned</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'signed',_'value':_'signed'}</t>
+          <t>signed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Signed', 'value': 'signed'}</t>
+          <t>Signed</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'unsigned',_'value':_'unsigned'}</t>
+          <t>unsigned</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Unsigned', 'value': 'unsigned'}</t>
+          <t>Unsigned</t>
         </is>
       </c>
     </row>
